--- a/results/main/Figure_2_data_meta_0p25_heterogeneity_0_multilevel_random.xlsx
+++ b/results/main/Figure_2_data_meta_0p25_heterogeneity_0_multilevel_random.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="748">
   <si>
     <t xml:space="preserve">cID</t>
   </si>
@@ -1818,6 +1818,9 @@
   </si>
   <si>
     <t xml:space="preserve">439-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">439-3</t>
   </si>
   <si>
     <t xml:space="preserve">439-4</t>
@@ -25672,13 +25675,13 @@
         <v>439</v>
       </c>
       <c r="C564" t="n">
-        <v>0.144890055686178</v>
+        <v>0.060956352796991</v>
       </c>
       <c r="D564" t="n">
         <v>0</v>
       </c>
       <c r="E564" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F564" t="s">
         <v>104</v>
@@ -25699,7 +25702,7 @@
         <v>15</v>
       </c>
       <c r="L564" t="n">
-        <v>14.49</v>
+        <v>6.1</v>
       </c>
       <c r="M564" t="n">
         <v>0</v>
@@ -25710,19 +25713,19 @@
         <v>603</v>
       </c>
       <c r="B565" t="n">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="C565" t="n">
-        <v>0.0673563456439499</v>
+        <v>0.144890055686178</v>
       </c>
       <c r="D565" t="n">
         <v>0</v>
       </c>
       <c r="E565" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F565" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="G565" t="s">
         <v>20</v>
@@ -25740,7 +25743,7 @@
         <v>15</v>
       </c>
       <c r="L565" t="n">
-        <v>6.74</v>
+        <v>14.49</v>
       </c>
       <c r="M565" t="n">
         <v>0</v>
@@ -25754,13 +25757,13 @@
         <v>460</v>
       </c>
       <c r="C566" t="n">
-        <v>0.0575795863734983</v>
+        <v>0.0673563456439499</v>
       </c>
       <c r="D566" t="n">
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="E566" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F566" t="s">
         <v>127</v>
@@ -25781,10 +25784,10 @@
         <v>15</v>
       </c>
       <c r="L566" t="n">
-        <v>5.76</v>
+        <v>6.74</v>
       </c>
       <c r="M566" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="567">
@@ -25795,13 +25798,13 @@
         <v>460</v>
       </c>
       <c r="C567" t="n">
-        <v>0.0501109958665532</v>
+        <v>0.0575795863734983</v>
       </c>
       <c r="D567" t="n">
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E567" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F567" t="s">
         <v>127</v>
@@ -25822,10 +25825,10 @@
         <v>15</v>
       </c>
       <c r="L567" t="n">
-        <v>5.01</v>
+        <v>5.76</v>
       </c>
       <c r="M567" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="568">
@@ -25836,16 +25839,16 @@
         <v>460</v>
       </c>
       <c r="C568" t="n">
-        <v>0.102866079117381</v>
+        <v>0.0501109958665532</v>
       </c>
       <c r="D568" t="n">
         <v>0</v>
       </c>
       <c r="E568" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F568" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="G568" t="s">
         <v>20</v>
@@ -25863,7 +25866,7 @@
         <v>15</v>
       </c>
       <c r="L568" t="n">
-        <v>10.29</v>
+        <v>5.01</v>
       </c>
       <c r="M568" t="n">
         <v>0</v>
@@ -25877,13 +25880,13 @@
         <v>460</v>
       </c>
       <c r="C569" t="n">
-        <v>0.251694883914456</v>
+        <v>0.102866079117381</v>
       </c>
       <c r="D569" t="n">
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="E569" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F569" t="s">
         <v>104</v>
@@ -25904,10 +25907,10 @@
         <v>15</v>
       </c>
       <c r="L569" t="n">
-        <v>25.17</v>
+        <v>10.29</v>
       </c>
       <c r="M569" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570">
@@ -25918,13 +25921,13 @@
         <v>460</v>
       </c>
       <c r="C570" t="n">
-        <v>0.1836284089659</v>
+        <v>0.251694883914456</v>
       </c>
       <c r="D570" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="E570" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F570" t="s">
         <v>104</v>
@@ -25945,10 +25948,10 @@
         <v>15</v>
       </c>
       <c r="L570" t="n">
-        <v>18.36</v>
+        <v>25.17</v>
       </c>
       <c r="M570" t="n">
-        <v>9.09</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="571">
@@ -25956,19 +25959,19 @@
         <v>609</v>
       </c>
       <c r="B571" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C571" t="n">
-        <v>0.152277384889428</v>
+        <v>0.1836284089659</v>
       </c>
       <c r="D571" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.0909090909090909</v>
       </c>
       <c r="E571" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F571" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G571" t="s">
         <v>20</v>
@@ -25977,19 +25980,19 @@
         <v>15</v>
       </c>
       <c r="I571" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J571" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K571" t="s">
         <v>15</v>
       </c>
       <c r="L571" t="n">
-        <v>15.23</v>
+        <v>18.36</v>
       </c>
       <c r="M571" t="n">
-        <v>4.17</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="572">
@@ -25997,19 +26000,19 @@
         <v>610</v>
       </c>
       <c r="B572" t="n">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="C572" t="n">
-        <v>0.117554922034053</v>
+        <v>0.152277384889428</v>
       </c>
       <c r="D572" t="n">
-        <v>0.2</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="E572" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F572" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G572" t="s">
         <v>20</v>
@@ -26018,19 +26021,19 @@
         <v>15</v>
       </c>
       <c r="I572" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J572" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K572" t="s">
         <v>15</v>
       </c>
       <c r="L572" t="n">
-        <v>11.76</v>
+        <v>15.23</v>
       </c>
       <c r="M572" t="n">
-        <v>20</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="573">
@@ -26038,19 +26041,19 @@
         <v>611</v>
       </c>
       <c r="B573" t="n">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C573" t="n">
-        <v>0.0510119255935755</v>
+        <v>0.117554922034053</v>
       </c>
       <c r="D573" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E573" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F573" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G573" t="s">
         <v>20</v>
@@ -26068,10 +26071,10 @@
         <v>15</v>
       </c>
       <c r="L573" t="n">
-        <v>5.1</v>
+        <v>11.76</v>
       </c>
       <c r="M573" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="574">
@@ -26082,7 +26085,7 @@
         <v>496</v>
       </c>
       <c r="C574" t="n">
-        <v>0.0588559594251462</v>
+        <v>0.0510119255935755</v>
       </c>
       <c r="D574" t="n">
         <v>0</v>
@@ -26109,7 +26112,7 @@
         <v>15</v>
       </c>
       <c r="L574" t="n">
-        <v>5.89</v>
+        <v>5.1</v>
       </c>
       <c r="M574" t="n">
         <v>0</v>
@@ -26120,19 +26123,19 @@
         <v>613</v>
       </c>
       <c r="B575" t="n">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C575" t="n">
-        <v>0.0612397538447644</v>
+        <v>0.0588559594251462</v>
       </c>
       <c r="D575" t="n">
         <v>0</v>
       </c>
       <c r="E575" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F575" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G575" t="s">
         <v>20</v>
@@ -26150,7 +26153,7 @@
         <v>15</v>
       </c>
       <c r="L575" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="M575" t="n">
         <v>0</v>
@@ -26164,7 +26167,7 @@
         <v>500</v>
       </c>
       <c r="C576" t="n">
-        <v>0.0797634776725735</v>
+        <v>0.0612397538447644</v>
       </c>
       <c r="D576" t="n">
         <v>0</v>
@@ -26191,7 +26194,7 @@
         <v>15</v>
       </c>
       <c r="L576" t="n">
-        <v>7.98</v>
+        <v>6.12</v>
       </c>
       <c r="M576" t="n">
         <v>0</v>
@@ -26205,13 +26208,13 @@
         <v>500</v>
       </c>
       <c r="C577" t="n">
-        <v>0.0545960369903362</v>
+        <v>0.0797634776725735</v>
       </c>
       <c r="D577" t="n">
         <v>0</v>
       </c>
       <c r="E577" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F577" t="s">
         <v>104</v>
@@ -26232,7 +26235,7 @@
         <v>15</v>
       </c>
       <c r="L577" t="n">
-        <v>5.46</v>
+        <v>7.98</v>
       </c>
       <c r="M577" t="n">
         <v>0</v>
@@ -26246,7 +26249,7 @@
         <v>500</v>
       </c>
       <c r="C578" t="n">
-        <v>0.0631622002673004</v>
+        <v>0.0545960369903362</v>
       </c>
       <c r="D578" t="n">
         <v>0</v>
@@ -26273,7 +26276,7 @@
         <v>15</v>
       </c>
       <c r="L578" t="n">
-        <v>6.32</v>
+        <v>5.46</v>
       </c>
       <c r="M578" t="n">
         <v>0</v>
@@ -26287,13 +26290,13 @@
         <v>500</v>
       </c>
       <c r="C579" t="n">
-        <v>0.0713851380910097</v>
+        <v>0.0631622002673004</v>
       </c>
       <c r="D579" t="n">
         <v>0</v>
       </c>
       <c r="E579" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F579" t="s">
         <v>104</v>
@@ -26314,7 +26317,7 @@
         <v>15</v>
       </c>
       <c r="L579" t="n">
-        <v>7.14</v>
+        <v>6.32</v>
       </c>
       <c r="M579" t="n">
         <v>0</v>
@@ -26325,28 +26328,28 @@
         <v>618</v>
       </c>
       <c r="B580" t="n">
-        <v>533</v>
+        <v>500</v>
       </c>
       <c r="C580" t="n">
-        <v>0.050584375900758</v>
+        <v>0.0713851380910097</v>
       </c>
       <c r="D580" t="n">
         <v>0</v>
       </c>
       <c r="E580" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F580" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G580" t="s">
         <v>20</v>
       </c>
       <c r="H580" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I580" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J580" t="s">
         <v>22</v>
@@ -26355,7 +26358,7 @@
         <v>15</v>
       </c>
       <c r="L580" t="n">
-        <v>5.06</v>
+        <v>7.14</v>
       </c>
       <c r="M580" t="n">
         <v>0</v>
@@ -26369,13 +26372,13 @@
         <v>533</v>
       </c>
       <c r="C581" t="n">
-        <v>0.0552651049152778</v>
+        <v>0.050584375900758</v>
       </c>
       <c r="D581" t="n">
         <v>0</v>
       </c>
       <c r="E581" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F581" t="s">
         <v>14</v>
@@ -26396,7 +26399,7 @@
         <v>15</v>
       </c>
       <c r="L581" t="n">
-        <v>5.53</v>
+        <v>5.06</v>
       </c>
       <c r="M581" t="n">
         <v>0</v>
@@ -26410,13 +26413,13 @@
         <v>533</v>
       </c>
       <c r="C582" t="n">
-        <v>0.0643008871452087</v>
+        <v>0.0552651049152778</v>
       </c>
       <c r="D582" t="n">
         <v>0</v>
       </c>
       <c r="E582" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F582" t="s">
         <v>14</v>
@@ -26437,7 +26440,7 @@
         <v>15</v>
       </c>
       <c r="L582" t="n">
-        <v>6.43</v>
+        <v>5.53</v>
       </c>
       <c r="M582" t="n">
         <v>0</v>
@@ -26451,13 +26454,13 @@
         <v>533</v>
       </c>
       <c r="C583" t="n">
-        <v>0.0503186662199912</v>
+        <v>0.0643008871452087</v>
       </c>
       <c r="D583" t="n">
         <v>0</v>
       </c>
       <c r="E583" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F583" t="s">
         <v>14</v>
@@ -26478,7 +26481,7 @@
         <v>15</v>
       </c>
       <c r="L583" t="n">
-        <v>5.03</v>
+        <v>6.43</v>
       </c>
       <c r="M583" t="n">
         <v>0</v>
@@ -26492,13 +26495,13 @@
         <v>533</v>
       </c>
       <c r="C584" t="n">
-        <v>0.0500163405392757</v>
+        <v>0.0503186662199912</v>
       </c>
       <c r="D584" t="n">
         <v>0</v>
       </c>
       <c r="E584" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F584" t="s">
         <v>14</v>
@@ -26519,7 +26522,7 @@
         <v>15</v>
       </c>
       <c r="L584" t="n">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="M584" t="n">
         <v>0</v>
@@ -26533,13 +26536,13 @@
         <v>533</v>
       </c>
       <c r="C585" t="n">
-        <v>0.0687196962234599</v>
+        <v>0.0500163405392757</v>
       </c>
       <c r="D585" t="n">
         <v>0</v>
       </c>
       <c r="E585" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F585" t="s">
         <v>14</v>
@@ -26560,7 +26563,7 @@
         <v>15</v>
       </c>
       <c r="L585" t="n">
-        <v>6.87</v>
+        <v>5</v>
       </c>
       <c r="M585" t="n">
         <v>0</v>
@@ -26574,13 +26577,13 @@
         <v>533</v>
       </c>
       <c r="C586" t="n">
-        <v>0.0509104347685849</v>
+        <v>0.0687196962234599</v>
       </c>
       <c r="D586" t="n">
         <v>0</v>
       </c>
       <c r="E586" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F586" t="s">
         <v>14</v>
@@ -26601,7 +26604,7 @@
         <v>15</v>
       </c>
       <c r="L586" t="n">
-        <v>5.09</v>
+        <v>6.87</v>
       </c>
       <c r="M586" t="n">
         <v>0</v>
@@ -26615,13 +26618,13 @@
         <v>533</v>
       </c>
       <c r="C587" t="n">
-        <v>0.0522468576177701</v>
+        <v>0.0509104347685849</v>
       </c>
       <c r="D587" t="n">
         <v>0</v>
       </c>
       <c r="E587" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F587" t="s">
         <v>14</v>
@@ -26642,7 +26645,7 @@
         <v>15</v>
       </c>
       <c r="L587" t="n">
-        <v>5.22</v>
+        <v>5.09</v>
       </c>
       <c r="M587" t="n">
         <v>0</v>
@@ -26653,40 +26656,40 @@
         <v>626</v>
       </c>
       <c r="B588" t="n">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C588" t="n">
-        <v>0.0601524168658118</v>
+        <v>0.0522468576177701</v>
       </c>
       <c r="D588" t="n">
-        <v>0.00302114803625378</v>
+        <v>0</v>
       </c>
       <c r="E588" t="n">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="F588" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G588" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H588" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I588" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J588" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K588" t="s">
         <v>15</v>
       </c>
       <c r="L588" t="n">
-        <v>6.02</v>
+        <v>5.22</v>
       </c>
       <c r="M588" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="589">
@@ -26694,16 +26697,16 @@
         <v>627</v>
       </c>
       <c r="B589" t="n">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C589" t="n">
-        <v>0.0736115213202643</v>
+        <v>0.0601524168658118</v>
       </c>
       <c r="D589" t="n">
-        <v>0.00987654320987654</v>
+        <v>0.00302114803625378</v>
       </c>
       <c r="E589" t="n">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="F589" t="s">
         <v>26</v>
@@ -26715,7 +26718,7 @@
         <v>15</v>
       </c>
       <c r="I589" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J589" t="s">
         <v>17</v>
@@ -26724,10 +26727,10 @@
         <v>15</v>
       </c>
       <c r="L589" t="n">
-        <v>7.36</v>
+        <v>6.02</v>
       </c>
       <c r="M589" t="n">
-        <v>0.99</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="590">
@@ -26738,13 +26741,13 @@
         <v>547</v>
       </c>
       <c r="C590" t="n">
-        <v>0.0530669819474756</v>
+        <v>0.0736115213202643</v>
       </c>
       <c r="D590" t="n">
-        <v>0</v>
+        <v>0.00987654320987654</v>
       </c>
       <c r="E590" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="F590" t="s">
         <v>26</v>
@@ -26765,10 +26768,10 @@
         <v>15</v>
       </c>
       <c r="L590" t="n">
-        <v>5.31</v>
+        <v>7.36</v>
       </c>
       <c r="M590" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="591">
@@ -26779,13 +26782,13 @@
         <v>547</v>
       </c>
       <c r="C591" t="n">
-        <v>0.114669240260331</v>
+        <v>0.0530669819474756</v>
       </c>
       <c r="D591" t="n">
-        <v>0.0404040404040404</v>
+        <v>0</v>
       </c>
       <c r="E591" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F591" t="s">
         <v>26</v>
@@ -26806,10 +26809,10 @@
         <v>15</v>
       </c>
       <c r="L591" t="n">
-        <v>11.47</v>
+        <v>5.31</v>
       </c>
       <c r="M591" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="592">
@@ -26820,13 +26823,13 @@
         <v>547</v>
       </c>
       <c r="C592" t="n">
-        <v>0.0502936774474025</v>
+        <v>0.114669240260331</v>
       </c>
       <c r="D592" t="n">
-        <v>0</v>
+        <v>0.0404040404040404</v>
       </c>
       <c r="E592" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F592" t="s">
         <v>26</v>
@@ -26847,10 +26850,10 @@
         <v>15</v>
       </c>
       <c r="L592" t="n">
-        <v>5.03</v>
+        <v>11.47</v>
       </c>
       <c r="M592" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="593">
@@ -26861,13 +26864,13 @@
         <v>547</v>
       </c>
       <c r="C593" t="n">
-        <v>0.0500796888300959</v>
+        <v>0.0502936774474025</v>
       </c>
       <c r="D593" t="n">
         <v>0</v>
       </c>
       <c r="E593" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F593" t="s">
         <v>26</v>
@@ -26888,7 +26891,7 @@
         <v>15</v>
       </c>
       <c r="L593" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
       <c r="M593" t="n">
         <v>0</v>
@@ -26902,13 +26905,13 @@
         <v>547</v>
       </c>
       <c r="C594" t="n">
-        <v>0.0501245404856183</v>
+        <v>0.0500796888300959</v>
       </c>
       <c r="D594" t="n">
         <v>0</v>
       </c>
       <c r="E594" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F594" t="s">
         <v>26</v>
@@ -26943,13 +26946,13 @@
         <v>547</v>
       </c>
       <c r="C595" t="n">
-        <v>0.0618949829056067</v>
+        <v>0.0501245404856183</v>
       </c>
       <c r="D595" t="n">
         <v>0</v>
       </c>
       <c r="E595" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="F595" t="s">
         <v>26</v>
@@ -26970,7 +26973,7 @@
         <v>15</v>
       </c>
       <c r="L595" t="n">
-        <v>6.19</v>
+        <v>5.01</v>
       </c>
       <c r="M595" t="n">
         <v>0</v>
@@ -26984,13 +26987,13 @@
         <v>547</v>
       </c>
       <c r="C596" t="n">
-        <v>0.0859434875718859</v>
+        <v>0.0618949829056067</v>
       </c>
       <c r="D596" t="n">
-        <v>0.0213903743315508</v>
+        <v>0</v>
       </c>
       <c r="E596" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F596" t="s">
         <v>26</v>
@@ -27011,10 +27014,10 @@
         <v>15</v>
       </c>
       <c r="L596" t="n">
-        <v>8.59</v>
+        <v>6.19</v>
       </c>
       <c r="M596" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="597">
@@ -27022,16 +27025,16 @@
         <v>635</v>
       </c>
       <c r="B597" t="n">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="C597" t="n">
-        <v>0.0772935675081238</v>
+        <v>0.0859434875718859</v>
       </c>
       <c r="D597" t="n">
-        <v>0.145161290322581</v>
+        <v>0.0213903743315508</v>
       </c>
       <c r="E597" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F597" t="s">
         <v>26</v>
@@ -27043,7 +27046,7 @@
         <v>15</v>
       </c>
       <c r="I597" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J597" t="s">
         <v>17</v>
@@ -27052,10 +27055,10 @@
         <v>15</v>
       </c>
       <c r="L597" t="n">
-        <v>7.73</v>
+        <v>8.59</v>
       </c>
       <c r="M597" t="n">
-        <v>14.52</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="598">
@@ -27066,13 +27069,13 @@
         <v>566</v>
       </c>
       <c r="C598" t="n">
-        <v>0.0503661356814811</v>
+        <v>0.0772935675081238</v>
       </c>
       <c r="D598" t="n">
-        <v>0</v>
+        <v>0.145161290322581</v>
       </c>
       <c r="E598" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F598" t="s">
         <v>26</v>
@@ -27093,10 +27096,10 @@
         <v>15</v>
       </c>
       <c r="L598" t="n">
-        <v>5.04</v>
+        <v>7.73</v>
       </c>
       <c r="M598" t="n">
-        <v>0</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="599">
@@ -27107,13 +27110,13 @@
         <v>566</v>
       </c>
       <c r="C599" t="n">
-        <v>0.0856131499294446</v>
+        <v>0.0503661356814811</v>
       </c>
       <c r="D599" t="n">
-        <v>0.0309278350515464</v>
+        <v>0</v>
       </c>
       <c r="E599" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F599" t="s">
         <v>26</v>
@@ -27134,10 +27137,10 @@
         <v>15</v>
       </c>
       <c r="L599" t="n">
-        <v>8.56</v>
+        <v>5.04</v>
       </c>
       <c r="M599" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="600">
@@ -27148,13 +27151,13 @@
         <v>566</v>
       </c>
       <c r="C600" t="n">
-        <v>0.728530335810601</v>
+        <v>0.0856131499294446</v>
       </c>
       <c r="D600" t="n">
-        <v>0.485074626865672</v>
+        <v>0.0309278350515464</v>
       </c>
       <c r="E600" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F600" t="s">
         <v>26</v>
@@ -27175,10 +27178,10 @@
         <v>15</v>
       </c>
       <c r="L600" t="n">
-        <v>72.85</v>
+        <v>8.56</v>
       </c>
       <c r="M600" t="n">
-        <v>48.51</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="601">
@@ -27189,13 +27192,13 @@
         <v>566</v>
       </c>
       <c r="C601" t="n">
-        <v>0.0759820819343286</v>
+        <v>0.728530335810601</v>
       </c>
       <c r="D601" t="n">
-        <v>0.107913669064748</v>
+        <v>0.485074626865672</v>
       </c>
       <c r="E601" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F601" t="s">
         <v>26</v>
@@ -27216,10 +27219,10 @@
         <v>15</v>
       </c>
       <c r="L601" t="n">
-        <v>7.6</v>
+        <v>72.85</v>
       </c>
       <c r="M601" t="n">
-        <v>10.79</v>
+        <v>48.51</v>
       </c>
     </row>
     <row r="602">
@@ -27230,13 +27233,13 @@
         <v>566</v>
       </c>
       <c r="C602" t="n">
-        <v>0.0550350876920489</v>
+        <v>0.0759820819343286</v>
       </c>
       <c r="D602" t="n">
-        <v>0</v>
+        <v>0.107913669064748</v>
       </c>
       <c r="E602" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F602" t="s">
         <v>26</v>
@@ -27257,10 +27260,10 @@
         <v>15</v>
       </c>
       <c r="L602" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="M602" t="n">
-        <v>0</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="603">
@@ -27271,13 +27274,13 @@
         <v>566</v>
       </c>
       <c r="C603" t="n">
-        <v>0.0531144626944244</v>
+        <v>0.0550350876920489</v>
       </c>
       <c r="D603" t="n">
         <v>0</v>
       </c>
       <c r="E603" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F603" t="s">
         <v>26</v>
@@ -27298,7 +27301,7 @@
         <v>15</v>
       </c>
       <c r="L603" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="M603" t="n">
         <v>0</v>
@@ -27312,13 +27315,13 @@
         <v>566</v>
       </c>
       <c r="C604" t="n">
-        <v>0.0620676485267885</v>
+        <v>0.0531144626944244</v>
       </c>
       <c r="D604" t="n">
         <v>0</v>
       </c>
       <c r="E604" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F604" t="s">
         <v>26</v>
@@ -27339,7 +27342,7 @@
         <v>15</v>
       </c>
       <c r="L604" t="n">
-        <v>6.21</v>
+        <v>5.31</v>
       </c>
       <c r="M604" t="n">
         <v>0</v>
@@ -27353,13 +27356,13 @@
         <v>566</v>
       </c>
       <c r="C605" t="n">
-        <v>0.0674956723006989</v>
+        <v>0.0620676485267885</v>
       </c>
       <c r="D605" t="n">
         <v>0</v>
       </c>
       <c r="E605" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="F605" t="s">
         <v>26</v>
@@ -27380,7 +27383,7 @@
         <v>15</v>
       </c>
       <c r="L605" t="n">
-        <v>6.75</v>
+        <v>6.21</v>
       </c>
       <c r="M605" t="n">
         <v>0</v>
@@ -27394,13 +27397,13 @@
         <v>566</v>
       </c>
       <c r="C606" t="n">
-        <v>0.0733392760556151</v>
+        <v>0.0674956723006989</v>
       </c>
       <c r="D606" t="n">
-        <v>0.135135135135135</v>
+        <v>0</v>
       </c>
       <c r="E606" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F606" t="s">
         <v>26</v>
@@ -27421,10 +27424,10 @@
         <v>15</v>
       </c>
       <c r="L606" t="n">
-        <v>7.33</v>
+        <v>6.75</v>
       </c>
       <c r="M606" t="n">
-        <v>13.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="607">
@@ -27435,13 +27438,13 @@
         <v>566</v>
       </c>
       <c r="C607" t="n">
-        <v>0.0583125364055228</v>
+        <v>0.0733392760556151</v>
       </c>
       <c r="D607" t="n">
-        <v>0</v>
+        <v>0.135135135135135</v>
       </c>
       <c r="E607" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F607" t="s">
         <v>26</v>
@@ -27462,10 +27465,10 @@
         <v>15</v>
       </c>
       <c r="L607" t="n">
-        <v>5.83</v>
+        <v>7.33</v>
       </c>
       <c r="M607" t="n">
-        <v>0</v>
+        <v>13.51</v>
       </c>
     </row>
     <row r="608">
@@ -27473,37 +27476,37 @@
         <v>646</v>
       </c>
       <c r="B608" t="n">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="C608" t="n">
-        <v>0.128496221490734</v>
+        <v>0.0583125364055228</v>
       </c>
       <c r="D608" t="n">
         <v>0</v>
       </c>
       <c r="E608" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F608" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G608" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H608" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I608" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J608" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K608" t="s">
         <v>15</v>
       </c>
       <c r="L608" t="n">
-        <v>12.85</v>
+        <v>5.83</v>
       </c>
       <c r="M608" t="n">
         <v>0</v>
@@ -27517,13 +27520,13 @@
         <v>581</v>
       </c>
       <c r="C609" t="n">
-        <v>0.0606802386092745</v>
+        <v>0.128496221490734</v>
       </c>
       <c r="D609" t="n">
         <v>0</v>
       </c>
       <c r="E609" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F609" t="s">
         <v>24</v>
@@ -27544,7 +27547,7 @@
         <v>15</v>
       </c>
       <c r="L609" t="n">
-        <v>6.07</v>
+        <v>12.85</v>
       </c>
       <c r="M609" t="n">
         <v>0</v>
@@ -27555,28 +27558,28 @@
         <v>648</v>
       </c>
       <c r="B610" t="n">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="C610" t="n">
-        <v>0.160414324196083</v>
+        <v>0.0606802386092745</v>
       </c>
       <c r="D610" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="E610" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F610" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G610" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H610" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I610" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J610" t="s">
         <v>22</v>
@@ -27585,10 +27588,10 @@
         <v>15</v>
       </c>
       <c r="L610" t="n">
-        <v>16.04</v>
+        <v>6.07</v>
       </c>
       <c r="M610" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
@@ -27599,13 +27602,13 @@
         <v>608</v>
       </c>
       <c r="C611" t="n">
-        <v>0.21833010782504</v>
+        <v>0.160414324196083</v>
       </c>
       <c r="D611" t="n">
-        <v>0.176470588235294</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E611" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F611" t="s">
         <v>19</v>
@@ -27626,10 +27629,10 @@
         <v>15</v>
       </c>
       <c r="L611" t="n">
-        <v>21.83</v>
+        <v>16.04</v>
       </c>
       <c r="M611" t="n">
-        <v>17.65</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="612">
@@ -27640,13 +27643,13 @@
         <v>608</v>
       </c>
       <c r="C612" t="n">
-        <v>0.999999999938752</v>
+        <v>0.21833010782504</v>
       </c>
       <c r="D612" t="n">
-        <v>0.545454545454545</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="E612" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F612" t="s">
         <v>19</v>
@@ -27664,13 +27667,13 @@
         <v>22</v>
       </c>
       <c r="K612" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L612" t="n">
-        <v>100</v>
+        <v>21.83</v>
       </c>
       <c r="M612" t="n">
-        <v>54.55</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="613">
@@ -27678,19 +27681,19 @@
         <v>651</v>
       </c>
       <c r="B613" t="n">
-        <v>62</v>
+        <v>608</v>
       </c>
       <c r="C613" t="n">
-        <v>0.068886859399625</v>
+        <v>0.999999999938752</v>
       </c>
       <c r="D613" t="n">
-        <v>0</v>
+        <v>0.545454545454545</v>
       </c>
       <c r="E613" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F613" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G613" t="s">
         <v>15</v>
@@ -27699,19 +27702,19 @@
         <v>15</v>
       </c>
       <c r="I613" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J613" t="s">
         <v>22</v>
       </c>
       <c r="K613" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L613" t="n">
-        <v>6.89</v>
+        <v>100</v>
       </c>
       <c r="M613" t="n">
-        <v>0</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="614">
@@ -27722,13 +27725,13 @@
         <v>62</v>
       </c>
       <c r="C614" t="n">
-        <v>0.0514357059568068</v>
+        <v>0.068886859399625</v>
       </c>
       <c r="D614" t="n">
         <v>0</v>
       </c>
       <c r="E614" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F614" t="s">
         <v>14</v>
@@ -27749,7 +27752,7 @@
         <v>15</v>
       </c>
       <c r="L614" t="n">
-        <v>5.14</v>
+        <v>6.89</v>
       </c>
       <c r="M614" t="n">
         <v>0</v>
@@ -27760,19 +27763,19 @@
         <v>653</v>
       </c>
       <c r="B615" t="n">
-        <v>623</v>
+        <v>62</v>
       </c>
       <c r="C615" t="n">
-        <v>0.052061182820237</v>
+        <v>0.0514357059568068</v>
       </c>
       <c r="D615" t="n">
         <v>0</v>
       </c>
       <c r="E615" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F615" t="s">
-        <v>393</v>
+        <v>14</v>
       </c>
       <c r="G615" t="s">
         <v>15</v>
@@ -27781,7 +27784,7 @@
         <v>15</v>
       </c>
       <c r="I615" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="J615" t="s">
         <v>22</v>
@@ -27790,7 +27793,7 @@
         <v>15</v>
       </c>
       <c r="L615" t="n">
-        <v>5.21</v>
+        <v>5.14</v>
       </c>
       <c r="M615" t="n">
         <v>0</v>
@@ -27804,13 +27807,13 @@
         <v>623</v>
       </c>
       <c r="C616" t="n">
-        <v>0.0614570089403204</v>
+        <v>0.052061182820237</v>
       </c>
       <c r="D616" t="n">
         <v>0</v>
       </c>
       <c r="E616" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F616" t="s">
         <v>393</v>
@@ -27831,7 +27834,7 @@
         <v>15</v>
       </c>
       <c r="L616" t="n">
-        <v>6.15</v>
+        <v>5.21</v>
       </c>
       <c r="M616" t="n">
         <v>0</v>
@@ -27842,19 +27845,19 @@
         <v>655</v>
       </c>
       <c r="B617" t="n">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C617" t="n">
-        <v>0.0682575998022078</v>
+        <v>0.0614570089403204</v>
       </c>
       <c r="D617" t="n">
-        <v>0.0661157024793388</v>
+        <v>0</v>
       </c>
       <c r="E617" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F617" t="s">
-        <v>26</v>
+        <v>393</v>
       </c>
       <c r="G617" t="s">
         <v>15</v>
@@ -27866,16 +27869,16 @@
         <v>34</v>
       </c>
       <c r="J617" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K617" t="s">
         <v>15</v>
       </c>
       <c r="L617" t="n">
-        <v>6.83</v>
+        <v>6.15</v>
       </c>
       <c r="M617" t="n">
-        <v>6.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="618">
@@ -27886,13 +27889,13 @@
         <v>624</v>
       </c>
       <c r="C618" t="n">
-        <v>0.0515849745378128</v>
+        <v>0.0682575998022078</v>
       </c>
       <c r="D618" t="n">
-        <v>0</v>
+        <v>0.0661157024793388</v>
       </c>
       <c r="E618" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="F618" t="s">
         <v>26</v>
@@ -27913,10 +27916,10 @@
         <v>15</v>
       </c>
       <c r="L618" t="n">
-        <v>5.16</v>
+        <v>6.83</v>
       </c>
       <c r="M618" t="n">
-        <v>0</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="619">
@@ -27927,13 +27930,13 @@
         <v>624</v>
       </c>
       <c r="C619" t="n">
-        <v>0.0592812030343327</v>
+        <v>0.0515849745378128</v>
       </c>
       <c r="D619" t="n">
-        <v>0.00558659217877095</v>
+        <v>0</v>
       </c>
       <c r="E619" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F619" t="s">
         <v>26</v>
@@ -27954,10 +27957,10 @@
         <v>15</v>
       </c>
       <c r="L619" t="n">
-        <v>5.93</v>
+        <v>5.16</v>
       </c>
       <c r="M619" t="n">
-        <v>0.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="620">
@@ -27965,40 +27968,40 @@
         <v>658</v>
       </c>
       <c r="B620" t="n">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C620" t="n">
-        <v>0.0595626128436594</v>
+        <v>0.0592812030343327</v>
       </c>
       <c r="D620" t="n">
-        <v>0</v>
+        <v>0.00558659217877095</v>
       </c>
       <c r="E620" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="F620" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="G620" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H620" t="s">
         <v>15</v>
       </c>
       <c r="I620" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J620" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K620" t="s">
         <v>15</v>
       </c>
       <c r="L620" t="n">
-        <v>5.96</v>
+        <v>5.93</v>
       </c>
       <c r="M620" t="n">
-        <v>0</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="621">
@@ -28009,13 +28012,13 @@
         <v>625</v>
       </c>
       <c r="C621" t="n">
-        <v>0.0725717275935162</v>
+        <v>0.0595626128436594</v>
       </c>
       <c r="D621" t="n">
-        <v>0.0273972602739726</v>
+        <v>0</v>
       </c>
       <c r="E621" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F621" t="s">
         <v>100</v>
@@ -28036,10 +28039,10 @@
         <v>15</v>
       </c>
       <c r="L621" t="n">
-        <v>7.26</v>
+        <v>5.96</v>
       </c>
       <c r="M621" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
@@ -28050,13 +28053,13 @@
         <v>625</v>
       </c>
       <c r="C622" t="n">
-        <v>0.059325212025788</v>
+        <v>0.0725717275935162</v>
       </c>
       <c r="D622" t="n">
-        <v>0</v>
+        <v>0.0273972602739726</v>
       </c>
       <c r="E622" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F622" t="s">
         <v>100</v>
@@ -28077,10 +28080,10 @@
         <v>15</v>
       </c>
       <c r="L622" t="n">
-        <v>5.93</v>
+        <v>7.26</v>
       </c>
       <c r="M622" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="623">
@@ -28088,19 +28091,19 @@
         <v>661</v>
       </c>
       <c r="B623" t="n">
-        <v>63</v>
+        <v>625</v>
       </c>
       <c r="C623" t="n">
-        <v>0.0523988195977709</v>
+        <v>0.059325212025788</v>
       </c>
       <c r="D623" t="n">
         <v>0</v>
       </c>
       <c r="E623" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F623" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G623" t="s">
         <v>20</v>
@@ -28118,7 +28121,7 @@
         <v>15</v>
       </c>
       <c r="L623" t="n">
-        <v>5.24</v>
+        <v>5.93</v>
       </c>
       <c r="M623" t="n">
         <v>0</v>
@@ -28132,13 +28135,13 @@
         <v>63</v>
       </c>
       <c r="C624" t="n">
-        <v>0.0506788433204808</v>
+        <v>0.0523988195977709</v>
       </c>
       <c r="D624" t="n">
         <v>0</v>
       </c>
       <c r="E624" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F624" t="s">
         <v>104</v>
@@ -28159,7 +28162,7 @@
         <v>15</v>
       </c>
       <c r="L624" t="n">
-        <v>5.07</v>
+        <v>5.24</v>
       </c>
       <c r="M624" t="n">
         <v>0</v>
@@ -28173,7 +28176,7 @@
         <v>63</v>
       </c>
       <c r="C625" t="n">
-        <v>0.0518550592322924</v>
+        <v>0.0506788433204808</v>
       </c>
       <c r="D625" t="n">
         <v>0</v>
@@ -28200,7 +28203,7 @@
         <v>15</v>
       </c>
       <c r="L625" t="n">
-        <v>5.19</v>
+        <v>5.07</v>
       </c>
       <c r="M625" t="n">
         <v>0</v>
@@ -28214,13 +28217,13 @@
         <v>63</v>
       </c>
       <c r="C626" t="n">
-        <v>0.0539175280774445</v>
+        <v>0.0518550592322924</v>
       </c>
       <c r="D626" t="n">
         <v>0</v>
       </c>
       <c r="E626" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F626" t="s">
         <v>104</v>
@@ -28241,7 +28244,7 @@
         <v>15</v>
       </c>
       <c r="L626" t="n">
-        <v>5.39</v>
+        <v>5.19</v>
       </c>
       <c r="M626" t="n">
         <v>0</v>
@@ -28255,13 +28258,13 @@
         <v>63</v>
       </c>
       <c r="C627" t="n">
-        <v>0.0500029906289887</v>
+        <v>0.0539175280774445</v>
       </c>
       <c r="D627" t="n">
         <v>0</v>
       </c>
       <c r="E627" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F627" t="s">
         <v>104</v>
@@ -28282,7 +28285,7 @@
         <v>15</v>
       </c>
       <c r="L627" t="n">
-        <v>5</v>
+        <v>5.39</v>
       </c>
       <c r="M627" t="n">
         <v>0</v>
@@ -28296,13 +28299,13 @@
         <v>63</v>
       </c>
       <c r="C628" t="n">
-        <v>0.0500630759064173</v>
+        <v>0.0500029906289887</v>
       </c>
       <c r="D628" t="n">
         <v>0</v>
       </c>
       <c r="E628" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F628" t="s">
         <v>104</v>
@@ -28323,7 +28326,7 @@
         <v>15</v>
       </c>
       <c r="L628" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="M628" t="n">
         <v>0</v>
@@ -28337,13 +28340,13 @@
         <v>63</v>
       </c>
       <c r="C629" t="n">
-        <v>0.0501151401873417</v>
+        <v>0.0500630759064173</v>
       </c>
       <c r="D629" t="n">
         <v>0</v>
       </c>
       <c r="E629" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F629" t="s">
         <v>104</v>
@@ -28378,13 +28381,13 @@
         <v>63</v>
       </c>
       <c r="C630" t="n">
-        <v>0.050120502352342</v>
+        <v>0.0501151401873417</v>
       </c>
       <c r="D630" t="n">
         <v>0</v>
       </c>
       <c r="E630" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F630" t="s">
         <v>104</v>
@@ -28419,13 +28422,13 @@
         <v>63</v>
       </c>
       <c r="C631" t="n">
-        <v>0.0503571486963985</v>
+        <v>0.050120502352342</v>
       </c>
       <c r="D631" t="n">
         <v>0</v>
       </c>
       <c r="E631" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F631" t="s">
         <v>104</v>
@@ -28446,7 +28449,7 @@
         <v>15</v>
       </c>
       <c r="L631" t="n">
-        <v>5.04</v>
+        <v>5.01</v>
       </c>
       <c r="M631" t="n">
         <v>0</v>
@@ -28460,13 +28463,13 @@
         <v>63</v>
       </c>
       <c r="C632" t="n">
-        <v>0.0519089469454182</v>
+        <v>0.0503571486963985</v>
       </c>
       <c r="D632" t="n">
         <v>0</v>
       </c>
       <c r="E632" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F632" t="s">
         <v>104</v>
@@ -28487,7 +28490,7 @@
         <v>15</v>
       </c>
       <c r="L632" t="n">
-        <v>5.19</v>
+        <v>5.04</v>
       </c>
       <c r="M632" t="n">
         <v>0</v>
@@ -28501,13 +28504,13 @@
         <v>63</v>
       </c>
       <c r="C633" t="n">
-        <v>0.0512097572853506</v>
+        <v>0.0519089469454182</v>
       </c>
       <c r="D633" t="n">
         <v>0</v>
       </c>
       <c r="E633" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F633" t="s">
         <v>104</v>
@@ -28528,7 +28531,7 @@
         <v>15</v>
       </c>
       <c r="L633" t="n">
-        <v>5.12</v>
+        <v>5.19</v>
       </c>
       <c r="M633" t="n">
         <v>0</v>
@@ -28542,13 +28545,13 @@
         <v>63</v>
       </c>
       <c r="C634" t="n">
-        <v>0.0505073844136684</v>
+        <v>0.0512097572853506</v>
       </c>
       <c r="D634" t="n">
         <v>0</v>
       </c>
       <c r="E634" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F634" t="s">
         <v>104</v>
@@ -28569,7 +28572,7 @@
         <v>15</v>
       </c>
       <c r="L634" t="n">
-        <v>5.05</v>
+        <v>5.12</v>
       </c>
       <c r="M634" t="n">
         <v>0</v>
@@ -28583,13 +28586,13 @@
         <v>63</v>
       </c>
       <c r="C635" t="n">
-        <v>0.0510001657691636</v>
+        <v>0.0505073844136684</v>
       </c>
       <c r="D635" t="n">
         <v>0</v>
       </c>
       <c r="E635" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F635" t="s">
         <v>104</v>
@@ -28610,7 +28613,7 @@
         <v>15</v>
       </c>
       <c r="L635" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="M635" t="n">
         <v>0</v>
@@ -28624,13 +28627,13 @@
         <v>63</v>
       </c>
       <c r="C636" t="n">
-        <v>0.0595292182563275</v>
+        <v>0.0510001657691636</v>
       </c>
       <c r="D636" t="n">
         <v>0</v>
       </c>
       <c r="E636" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F636" t="s">
         <v>104</v>
@@ -28651,7 +28654,7 @@
         <v>15</v>
       </c>
       <c r="L636" t="n">
-        <v>5.95</v>
+        <v>5.1</v>
       </c>
       <c r="M636" t="n">
         <v>0</v>
@@ -28665,13 +28668,13 @@
         <v>63</v>
       </c>
       <c r="C637" t="n">
-        <v>0.0549736667374269</v>
+        <v>0.0595292182563275</v>
       </c>
       <c r="D637" t="n">
         <v>0</v>
       </c>
       <c r="E637" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F637" t="s">
         <v>104</v>
@@ -28692,7 +28695,7 @@
         <v>15</v>
       </c>
       <c r="L637" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="M637" t="n">
         <v>0</v>
@@ -28706,13 +28709,13 @@
         <v>63</v>
       </c>
       <c r="C638" t="n">
-        <v>0.0503564254264557</v>
+        <v>0.0549736667374269</v>
       </c>
       <c r="D638" t="n">
         <v>0</v>
       </c>
       <c r="E638" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F638" t="s">
         <v>104</v>
@@ -28733,7 +28736,7 @@
         <v>15</v>
       </c>
       <c r="L638" t="n">
-        <v>5.04</v>
+        <v>5.5</v>
       </c>
       <c r="M638" t="n">
         <v>0</v>
@@ -28747,13 +28750,13 @@
         <v>63</v>
       </c>
       <c r="C639" t="n">
-        <v>0.0512203272881844</v>
+        <v>0.0503564254264557</v>
       </c>
       <c r="D639" t="n">
         <v>0</v>
       </c>
       <c r="E639" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F639" t="s">
         <v>104</v>
@@ -28774,7 +28777,7 @@
         <v>15</v>
       </c>
       <c r="L639" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="M639" t="n">
         <v>0</v>
@@ -28788,13 +28791,13 @@
         <v>63</v>
       </c>
       <c r="C640" t="n">
-        <v>0.0542994362952716</v>
+        <v>0.0512203272881844</v>
       </c>
       <c r="D640" t="n">
         <v>0</v>
       </c>
       <c r="E640" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F640" t="s">
         <v>104</v>
@@ -28815,7 +28818,7 @@
         <v>15</v>
       </c>
       <c r="L640" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="M640" t="n">
         <v>0</v>
@@ -28829,13 +28832,13 @@
         <v>63</v>
       </c>
       <c r="C641" t="n">
-        <v>0.0502115867131796</v>
+        <v>0.0542994362952716</v>
       </c>
       <c r="D641" t="n">
         <v>0</v>
       </c>
       <c r="E641" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F641" t="s">
         <v>104</v>
@@ -28856,7 +28859,7 @@
         <v>15</v>
       </c>
       <c r="L641" t="n">
-        <v>5.02</v>
+        <v>5.43</v>
       </c>
       <c r="M641" t="n">
         <v>0</v>
@@ -28870,13 +28873,13 @@
         <v>63</v>
       </c>
       <c r="C642" t="n">
-        <v>0.0614695114474159</v>
+        <v>0.0502115867131796</v>
       </c>
       <c r="D642" t="n">
         <v>0</v>
       </c>
       <c r="E642" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F642" t="s">
         <v>104</v>
@@ -28897,7 +28900,7 @@
         <v>15</v>
       </c>
       <c r="L642" t="n">
-        <v>6.15</v>
+        <v>5.02</v>
       </c>
       <c r="M642" t="n">
         <v>0</v>
@@ -28911,7 +28914,7 @@
         <v>63</v>
       </c>
       <c r="C643" t="n">
-        <v>0.0524387659150146</v>
+        <v>0.0614695114474159</v>
       </c>
       <c r="D643" t="n">
         <v>0</v>
@@ -28938,7 +28941,7 @@
         <v>15</v>
       </c>
       <c r="L643" t="n">
-        <v>5.24</v>
+        <v>6.15</v>
       </c>
       <c r="M643" t="n">
         <v>0</v>
@@ -28952,13 +28955,13 @@
         <v>63</v>
       </c>
       <c r="C644" t="n">
-        <v>0.0535163591653429</v>
+        <v>0.0524387659150146</v>
       </c>
       <c r="D644" t="n">
         <v>0</v>
       </c>
       <c r="E644" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F644" t="s">
         <v>104</v>
@@ -28979,7 +28982,7 @@
         <v>15</v>
       </c>
       <c r="L644" t="n">
-        <v>5.35</v>
+        <v>5.24</v>
       </c>
       <c r="M644" t="n">
         <v>0</v>
@@ -28993,13 +28996,13 @@
         <v>63</v>
       </c>
       <c r="C645" t="n">
-        <v>0.0511627845566788</v>
+        <v>0.0535163591653429</v>
       </c>
       <c r="D645" t="n">
         <v>0</v>
       </c>
       <c r="E645" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F645" t="s">
         <v>104</v>
@@ -29020,7 +29023,7 @@
         <v>15</v>
       </c>
       <c r="L645" t="n">
-        <v>5.12</v>
+        <v>5.35</v>
       </c>
       <c r="M645" t="n">
         <v>0</v>
@@ -29031,37 +29034,37 @@
         <v>684</v>
       </c>
       <c r="B646" t="n">
-        <v>651</v>
+        <v>63</v>
       </c>
       <c r="C646" t="n">
-        <v>0.0591588468663489</v>
+        <v>0.0511627845566788</v>
       </c>
       <c r="D646" t="n">
         <v>0</v>
       </c>
       <c r="E646" t="n">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="F646" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G646" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H646" t="s">
         <v>15</v>
       </c>
       <c r="I646" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J646" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K646" t="s">
         <v>15</v>
       </c>
       <c r="L646" t="n">
-        <v>5.92</v>
+        <v>5.12</v>
       </c>
       <c r="M646" t="n">
         <v>0</v>
@@ -29072,37 +29075,37 @@
         <v>685</v>
       </c>
       <c r="B647" t="n">
-        <v>715</v>
+        <v>651</v>
       </c>
       <c r="C647" t="n">
-        <v>0.0598543909500397</v>
+        <v>0.0591588468663489</v>
       </c>
       <c r="D647" t="n">
         <v>0</v>
       </c>
       <c r="E647" t="n">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="F647" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="G647" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H647" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I647" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J647" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K647" t="s">
         <v>15</v>
       </c>
       <c r="L647" t="n">
-        <v>5.99</v>
+        <v>5.92</v>
       </c>
       <c r="M647" t="n">
         <v>0</v>
@@ -29116,13 +29119,13 @@
         <v>715</v>
       </c>
       <c r="C648" t="n">
-        <v>0.0628376763034786</v>
+        <v>0.0598543909500397</v>
       </c>
       <c r="D648" t="n">
         <v>0</v>
       </c>
       <c r="E648" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F648" t="s">
         <v>127</v>
@@ -29143,7 +29146,7 @@
         <v>15</v>
       </c>
       <c r="L648" t="n">
-        <v>6.28</v>
+        <v>5.99</v>
       </c>
       <c r="M648" t="n">
         <v>0</v>
@@ -29157,7 +29160,7 @@
         <v>715</v>
       </c>
       <c r="C649" t="n">
-        <v>0.052763937637357</v>
+        <v>0.0628376763034786</v>
       </c>
       <c r="D649" t="n">
         <v>0</v>
@@ -29184,7 +29187,7 @@
         <v>15</v>
       </c>
       <c r="L649" t="n">
-        <v>5.28</v>
+        <v>6.28</v>
       </c>
       <c r="M649" t="n">
         <v>0</v>
@@ -29195,37 +29198,37 @@
         <v>688</v>
       </c>
       <c r="B650" t="n">
-        <v>753</v>
+        <v>715</v>
       </c>
       <c r="C650" t="n">
-        <v>0.0567779274338602</v>
+        <v>0.052763937637357</v>
       </c>
       <c r="D650" t="n">
         <v>0</v>
       </c>
       <c r="E650" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F650" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="G650" t="s">
         <v>20</v>
       </c>
       <c r="H650" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I650" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="J650" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K650" t="s">
         <v>15</v>
       </c>
       <c r="L650" t="n">
-        <v>5.68</v>
+        <v>5.28</v>
       </c>
       <c r="M650" t="n">
         <v>0</v>
@@ -29239,7 +29242,7 @@
         <v>753</v>
       </c>
       <c r="C651" t="n">
-        <v>0.0500801905895531</v>
+        <v>0.0567779274338602</v>
       </c>
       <c r="D651" t="n">
         <v>0</v>
@@ -29266,7 +29269,7 @@
         <v>15</v>
       </c>
       <c r="L651" t="n">
-        <v>5.01</v>
+        <v>5.68</v>
       </c>
       <c r="M651" t="n">
         <v>0</v>
@@ -29280,7 +29283,7 @@
         <v>753</v>
       </c>
       <c r="C652" t="n">
-        <v>0.0520023813147518</v>
+        <v>0.0500801905895531</v>
       </c>
       <c r="D652" t="n">
         <v>0</v>
@@ -29307,7 +29310,7 @@
         <v>15</v>
       </c>
       <c r="L652" t="n">
-        <v>5.2</v>
+        <v>5.01</v>
       </c>
       <c r="M652" t="n">
         <v>0</v>
@@ -29321,7 +29324,7 @@
         <v>753</v>
       </c>
       <c r="C653" t="n">
-        <v>0.0517693629382255</v>
+        <v>0.0520023813147518</v>
       </c>
       <c r="D653" t="n">
         <v>0</v>
@@ -29348,7 +29351,7 @@
         <v>15</v>
       </c>
       <c r="L653" t="n">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
       <c r="M653" t="n">
         <v>0</v>
@@ -29362,7 +29365,7 @@
         <v>753</v>
       </c>
       <c r="C654" t="n">
-        <v>0.0936883453219992</v>
+        <v>0.0517693629382255</v>
       </c>
       <c r="D654" t="n">
         <v>0</v>
@@ -29389,7 +29392,7 @@
         <v>15</v>
       </c>
       <c r="L654" t="n">
-        <v>9.37</v>
+        <v>5.18</v>
       </c>
       <c r="M654" t="n">
         <v>0</v>
@@ -29400,22 +29403,22 @@
         <v>693</v>
       </c>
       <c r="B655" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C655" t="n">
-        <v>0.0808341151859053</v>
+        <v>0.0936883453219992</v>
       </c>
       <c r="D655" t="n">
         <v>0</v>
       </c>
       <c r="E655" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F655" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G655" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H655" t="s">
         <v>15</v>
@@ -29424,13 +29427,13 @@
         <v>46</v>
       </c>
       <c r="J655" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K655" t="s">
         <v>15</v>
       </c>
       <c r="L655" t="n">
-        <v>8.08</v>
+        <v>9.37</v>
       </c>
       <c r="M655" t="n">
         <v>0</v>
@@ -29441,19 +29444,19 @@
         <v>694</v>
       </c>
       <c r="B656" t="n">
-        <v>813</v>
+        <v>755</v>
       </c>
       <c r="C656" t="n">
-        <v>0.0516824953252925</v>
+        <v>0.0808341151859053</v>
       </c>
       <c r="D656" t="n">
         <v>0</v>
       </c>
       <c r="E656" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F656" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G656" t="s">
         <v>15</v>
@@ -29462,16 +29465,16 @@
         <v>15</v>
       </c>
       <c r="I656" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="J656" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K656" t="s">
         <v>15</v>
       </c>
       <c r="L656" t="n">
-        <v>5.17</v>
+        <v>8.08</v>
       </c>
       <c r="M656" t="n">
         <v>0</v>
@@ -29485,13 +29488,13 @@
         <v>813</v>
       </c>
       <c r="C657" t="n">
-        <v>0.0601895974501842</v>
+        <v>0.0516824953252925</v>
       </c>
       <c r="D657" t="n">
         <v>0</v>
       </c>
       <c r="E657" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="F657" t="s">
         <v>104</v>
@@ -29512,7 +29515,7 @@
         <v>15</v>
       </c>
       <c r="L657" t="n">
-        <v>6.02</v>
+        <v>5.17</v>
       </c>
       <c r="M657" t="n">
         <v>0</v>
@@ -29526,16 +29529,16 @@
         <v>813</v>
       </c>
       <c r="C658" t="n">
-        <v>0.0535289221649116</v>
+        <v>0.0601895974501842</v>
       </c>
       <c r="D658" t="n">
         <v>0</v>
       </c>
       <c r="E658" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F658" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G658" t="s">
         <v>15</v>
@@ -29553,7 +29556,7 @@
         <v>15</v>
       </c>
       <c r="L658" t="n">
-        <v>5.35</v>
+        <v>6.02</v>
       </c>
       <c r="M658" t="n">
         <v>0</v>
@@ -29564,19 +29567,19 @@
         <v>697</v>
       </c>
       <c r="B659" t="n">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C659" t="n">
-        <v>0.080783823777224</v>
+        <v>0.0535289221649116</v>
       </c>
       <c r="D659" t="n">
         <v>0</v>
       </c>
       <c r="E659" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F659" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G659" t="s">
         <v>15</v>
@@ -29585,7 +29588,7 @@
         <v>15</v>
       </c>
       <c r="I659" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="J659" t="s">
         <v>17</v>
@@ -29594,7 +29597,7 @@
         <v>15</v>
       </c>
       <c r="L659" t="n">
-        <v>8.08</v>
+        <v>5.35</v>
       </c>
       <c r="M659" t="n">
         <v>0</v>
@@ -29608,13 +29611,13 @@
         <v>816</v>
       </c>
       <c r="C660" t="n">
-        <v>0.107195055508188</v>
+        <v>0.080783823777224</v>
       </c>
       <c r="D660" t="n">
         <v>0</v>
       </c>
       <c r="E660" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F660" t="s">
         <v>26</v>
@@ -29635,7 +29638,7 @@
         <v>15</v>
       </c>
       <c r="L660" t="n">
-        <v>10.72</v>
+        <v>8.08</v>
       </c>
       <c r="M660" t="n">
         <v>0</v>
@@ -29646,10 +29649,10 @@
         <v>699</v>
       </c>
       <c r="B661" t="n">
-        <v>83</v>
+        <v>816</v>
       </c>
       <c r="C661" t="n">
-        <v>0.0514764469127019</v>
+        <v>0.107195055508188</v>
       </c>
       <c r="D661" t="n">
         <v>0</v>
@@ -29658,25 +29661,25 @@
         <v>5</v>
       </c>
       <c r="F661" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="G661" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H661" t="s">
         <v>15</v>
       </c>
       <c r="I661" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J661" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K661" t="s">
         <v>15</v>
       </c>
       <c r="L661" t="n">
-        <v>5.15</v>
+        <v>10.72</v>
       </c>
       <c r="M661" t="n">
         <v>0</v>
@@ -29690,13 +29693,13 @@
         <v>83</v>
       </c>
       <c r="C662" t="n">
-        <v>0.0507780193351134</v>
+        <v>0.0514764469127019</v>
       </c>
       <c r="D662" t="n">
         <v>0</v>
       </c>
       <c r="E662" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F662" t="s">
         <v>104</v>
@@ -29717,7 +29720,7 @@
         <v>15</v>
       </c>
       <c r="L662" t="n">
-        <v>5.08</v>
+        <v>5.15</v>
       </c>
       <c r="M662" t="n">
         <v>0</v>
@@ -29728,16 +29731,16 @@
         <v>701</v>
       </c>
       <c r="B663" t="n">
-        <v>847</v>
+        <v>83</v>
       </c>
       <c r="C663" t="n">
-        <v>0.0869611289804357</v>
+        <v>0.0507780193351134</v>
       </c>
       <c r="D663" t="n">
         <v>0</v>
       </c>
       <c r="E663" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F663" t="s">
         <v>104</v>
@@ -29758,7 +29761,7 @@
         <v>15</v>
       </c>
       <c r="L663" t="n">
-        <v>8.7</v>
+        <v>5.08</v>
       </c>
       <c r="M663" t="n">
         <v>0</v>
@@ -29772,16 +29775,16 @@
         <v>847</v>
       </c>
       <c r="C664" t="n">
-        <v>0.0813561327927215</v>
+        <v>0.0869611289804357</v>
       </c>
       <c r="D664" t="n">
         <v>0</v>
       </c>
       <c r="E664" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F664" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="G664" t="s">
         <v>20</v>
@@ -29799,7 +29802,7 @@
         <v>15</v>
       </c>
       <c r="L664" t="n">
-        <v>8.14</v>
+        <v>8.7</v>
       </c>
       <c r="M664" t="n">
         <v>0</v>
@@ -29810,19 +29813,19 @@
         <v>703</v>
       </c>
       <c r="B665" t="n">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C665" t="n">
-        <v>0.0851150149197209</v>
+        <v>0.0813561327927215</v>
       </c>
       <c r="D665" t="n">
         <v>0</v>
       </c>
       <c r="E665" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F665" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="G665" t="s">
         <v>20</v>
@@ -29831,7 +29834,7 @@
         <v>15</v>
       </c>
       <c r="I665" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J665" t="s">
         <v>22</v>
@@ -29840,7 +29843,7 @@
         <v>15</v>
       </c>
       <c r="L665" t="n">
-        <v>8.51</v>
+        <v>8.14</v>
       </c>
       <c r="M665" t="n">
         <v>0</v>
@@ -29854,13 +29857,13 @@
         <v>849</v>
       </c>
       <c r="C666" t="n">
-        <v>0.0521103080453202</v>
+        <v>0.0851150149197209</v>
       </c>
       <c r="D666" t="n">
         <v>0</v>
       </c>
       <c r="E666" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F666" t="s">
         <v>100</v>
@@ -29881,7 +29884,7 @@
         <v>15</v>
       </c>
       <c r="L666" t="n">
-        <v>5.21</v>
+        <v>8.51</v>
       </c>
       <c r="M666" t="n">
         <v>0</v>
@@ -29895,13 +29898,13 @@
         <v>849</v>
       </c>
       <c r="C667" t="n">
-        <v>0.0531298023360322</v>
+        <v>0.0521103080453202</v>
       </c>
       <c r="D667" t="n">
         <v>0</v>
       </c>
       <c r="E667" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F667" t="s">
         <v>100</v>
@@ -29922,7 +29925,7 @@
         <v>15</v>
       </c>
       <c r="L667" t="n">
-        <v>5.31</v>
+        <v>5.21</v>
       </c>
       <c r="M667" t="n">
         <v>0</v>
@@ -29933,19 +29936,19 @@
         <v>706</v>
       </c>
       <c r="B668" t="n">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C668" t="n">
-        <v>0.133170678157746</v>
+        <v>0.0531298023360322</v>
       </c>
       <c r="D668" t="n">
         <v>0</v>
       </c>
       <c r="E668" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F668" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="G668" t="s">
         <v>20</v>
@@ -29954,7 +29957,7 @@
         <v>15</v>
       </c>
       <c r="I668" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J668" t="s">
         <v>22</v>
@@ -29963,7 +29966,7 @@
         <v>15</v>
       </c>
       <c r="L668" t="n">
-        <v>13.32</v>
+        <v>5.31</v>
       </c>
       <c r="M668" t="n">
         <v>0</v>
@@ -29977,7 +29980,7 @@
         <v>850</v>
       </c>
       <c r="C669" t="n">
-        <v>0.0515209251391694</v>
+        <v>0.133170678157746</v>
       </c>
       <c r="D669" t="n">
         <v>0</v>
@@ -29986,7 +29989,7 @@
         <v>6</v>
       </c>
       <c r="F669" t="s">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="G669" t="s">
         <v>20</v>
@@ -30004,7 +30007,7 @@
         <v>15</v>
       </c>
       <c r="L669" t="n">
-        <v>5.15</v>
+        <v>13.32</v>
       </c>
       <c r="M669" t="n">
         <v>0</v>
@@ -30015,19 +30018,19 @@
         <v>708</v>
       </c>
       <c r="B670" t="n">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C670" t="n">
-        <v>0.0539577799195214</v>
+        <v>0.0515209251391694</v>
       </c>
       <c r="D670" t="n">
         <v>0</v>
       </c>
       <c r="E670" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F670" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="G670" t="s">
         <v>20</v>
@@ -30036,7 +30039,7 @@
         <v>15</v>
       </c>
       <c r="I670" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J670" t="s">
         <v>22</v>
@@ -30045,7 +30048,7 @@
         <v>15</v>
       </c>
       <c r="L670" t="n">
-        <v>5.4</v>
+        <v>5.15</v>
       </c>
       <c r="M670" t="n">
         <v>0</v>
@@ -30059,13 +30062,13 @@
         <v>855</v>
       </c>
       <c r="C671" t="n">
-        <v>0.0936150898634315</v>
+        <v>0.0539577799195214</v>
       </c>
       <c r="D671" t="n">
         <v>0</v>
       </c>
       <c r="E671" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="F671" t="s">
         <v>33</v>
@@ -30086,7 +30089,7 @@
         <v>15</v>
       </c>
       <c r="L671" t="n">
-        <v>9.36</v>
+        <v>5.4</v>
       </c>
       <c r="M671" t="n">
         <v>0</v>
@@ -30100,13 +30103,13 @@
         <v>855</v>
       </c>
       <c r="C672" t="n">
-        <v>0.0907870585757285</v>
+        <v>0.0936150898634315</v>
       </c>
       <c r="D672" t="n">
         <v>0</v>
       </c>
       <c r="E672" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F672" t="s">
         <v>33</v>
@@ -30127,7 +30130,7 @@
         <v>15</v>
       </c>
       <c r="L672" t="n">
-        <v>9.08</v>
+        <v>9.36</v>
       </c>
       <c r="M672" t="n">
         <v>0</v>
@@ -30141,13 +30144,13 @@
         <v>855</v>
       </c>
       <c r="C673" t="n">
-        <v>0.0639081363605964</v>
+        <v>0.0907870585757285</v>
       </c>
       <c r="D673" t="n">
         <v>0</v>
       </c>
       <c r="E673" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F673" t="s">
         <v>33</v>
@@ -30168,7 +30171,7 @@
         <v>15</v>
       </c>
       <c r="L673" t="n">
-        <v>6.39</v>
+        <v>9.08</v>
       </c>
       <c r="M673" t="n">
         <v>0</v>
@@ -30179,19 +30182,19 @@
         <v>712</v>
       </c>
       <c r="B674" t="n">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="C674" t="n">
-        <v>0.0724675500681863</v>
+        <v>0.0639081363605964</v>
       </c>
       <c r="D674" t="n">
         <v>0</v>
       </c>
       <c r="E674" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F674" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G674" t="s">
         <v>20</v>
@@ -30200,7 +30203,7 @@
         <v>15</v>
       </c>
       <c r="I674" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J674" t="s">
         <v>22</v>
@@ -30209,7 +30212,7 @@
         <v>15</v>
       </c>
       <c r="L674" t="n">
-        <v>7.25</v>
+        <v>6.39</v>
       </c>
       <c r="M674" t="n">
         <v>0</v>
@@ -30223,13 +30226,13 @@
         <v>871</v>
       </c>
       <c r="C675" t="n">
-        <v>0.067764137113927</v>
+        <v>0.0724675500681863</v>
       </c>
       <c r="D675" t="n">
         <v>0</v>
       </c>
       <c r="E675" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F675" t="s">
         <v>24</v>
@@ -30250,7 +30253,7 @@
         <v>15</v>
       </c>
       <c r="L675" t="n">
-        <v>6.78</v>
+        <v>7.25</v>
       </c>
       <c r="M675" t="n">
         <v>0</v>
@@ -30264,13 +30267,13 @@
         <v>871</v>
       </c>
       <c r="C676" t="n">
-        <v>0.0523391919187976</v>
+        <v>0.067764137113927</v>
       </c>
       <c r="D676" t="n">
         <v>0</v>
       </c>
       <c r="E676" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F676" t="s">
         <v>24</v>
@@ -30291,7 +30294,7 @@
         <v>15</v>
       </c>
       <c r="L676" t="n">
-        <v>5.23</v>
+        <v>6.78</v>
       </c>
       <c r="M676" t="n">
         <v>0</v>
@@ -30302,37 +30305,37 @@
         <v>715</v>
       </c>
       <c r="B677" t="n">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="C677" t="n">
-        <v>0.0583507313767999</v>
+        <v>0.0523391919187976</v>
       </c>
       <c r="D677" t="n">
         <v>0</v>
       </c>
       <c r="E677" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F677" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G677" t="s">
         <v>20</v>
       </c>
       <c r="H677" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I677" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J677" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K677" t="s">
         <v>15</v>
       </c>
       <c r="L677" t="n">
-        <v>5.84</v>
+        <v>5.23</v>
       </c>
       <c r="M677" t="n">
         <v>0</v>
@@ -30346,13 +30349,13 @@
         <v>877</v>
       </c>
       <c r="C678" t="n">
-        <v>0.0611932937077046</v>
+        <v>0.0583507313767999</v>
       </c>
       <c r="D678" t="n">
         <v>0</v>
       </c>
       <c r="E678" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F678" t="s">
         <v>33</v>
@@ -30373,7 +30376,7 @@
         <v>15</v>
       </c>
       <c r="L678" t="n">
-        <v>6.12</v>
+        <v>5.84</v>
       </c>
       <c r="M678" t="n">
         <v>0</v>
@@ -30384,37 +30387,37 @@
         <v>717</v>
       </c>
       <c r="B679" t="n">
-        <v>908</v>
+        <v>877</v>
       </c>
       <c r="C679" t="n">
-        <v>0.178736097621261</v>
+        <v>0.0611932937077046</v>
       </c>
       <c r="D679" t="n">
         <v>0</v>
       </c>
       <c r="E679" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F679" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="G679" t="s">
         <v>20</v>
       </c>
       <c r="H679" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I679" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J679" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K679" t="s">
         <v>15</v>
       </c>
       <c r="L679" t="n">
-        <v>17.87</v>
+        <v>6.12</v>
       </c>
       <c r="M679" t="n">
         <v>0</v>
@@ -30425,19 +30428,19 @@
         <v>718</v>
       </c>
       <c r="B680" t="n">
-        <v>91</v>
+        <v>908</v>
       </c>
       <c r="C680" t="n">
-        <v>1</v>
+        <v>0.178736097621261</v>
       </c>
       <c r="D680" t="n">
-        <v>0.734615384615385</v>
+        <v>0</v>
       </c>
       <c r="E680" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F680" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="G680" t="s">
         <v>20</v>
@@ -30449,16 +30452,16 @@
         <v>21</v>
       </c>
       <c r="J680" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K680" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L680" t="n">
-        <v>100</v>
+        <v>17.87</v>
       </c>
       <c r="M680" t="n">
-        <v>73.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="681">
@@ -30469,13 +30472,13 @@
         <v>91</v>
       </c>
       <c r="C681" t="n">
-        <v>0.948911921441842</v>
+        <v>1</v>
       </c>
       <c r="D681" t="n">
-        <v>0.529900332225914</v>
+        <v>0.734615384615385</v>
       </c>
       <c r="E681" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="F681" t="s">
         <v>26</v>
@@ -30496,10 +30499,10 @@
         <v>20</v>
       </c>
       <c r="L681" t="n">
-        <v>94.89</v>
+        <v>100</v>
       </c>
       <c r="M681" t="n">
-        <v>52.99</v>
+        <v>73.46</v>
       </c>
     </row>
     <row r="682">
@@ -30510,13 +30513,13 @@
         <v>91</v>
       </c>
       <c r="C682" t="n">
-        <v>1</v>
+        <v>0.948911921441842</v>
       </c>
       <c r="D682" t="n">
-        <v>0.970588235294118</v>
+        <v>0.529900332225914</v>
       </c>
       <c r="E682" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F682" t="s">
         <v>26</v>
@@ -30537,10 +30540,10 @@
         <v>20</v>
       </c>
       <c r="L682" t="n">
-        <v>100</v>
+        <v>94.89</v>
       </c>
       <c r="M682" t="n">
-        <v>97.06</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="683">
@@ -30554,10 +30557,10 @@
         <v>1</v>
       </c>
       <c r="D683" t="n">
-        <v>0.645161290322581</v>
+        <v>0.970588235294118</v>
       </c>
       <c r="E683" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="F683" t="s">
         <v>26</v>
@@ -30581,7 +30584,7 @@
         <v>100</v>
       </c>
       <c r="M683" t="n">
-        <v>64.52</v>
+        <v>97.06</v>
       </c>
     </row>
     <row r="684">
@@ -30592,13 +30595,13 @@
         <v>91</v>
       </c>
       <c r="C684" t="n">
-        <v>0.999999999999998</v>
+        <v>1</v>
       </c>
       <c r="D684" t="n">
-        <v>0.688888888888889</v>
+        <v>0.645161290322581</v>
       </c>
       <c r="E684" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F684" t="s">
         <v>26</v>
@@ -30622,7 +30625,7 @@
         <v>100</v>
       </c>
       <c r="M684" t="n">
-        <v>68.89</v>
+        <v>64.52</v>
       </c>
     </row>
     <row r="685">
@@ -30633,13 +30636,13 @@
         <v>91</v>
       </c>
       <c r="C685" t="n">
-        <v>0.999998657204063</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="D685" t="n">
-        <v>0.687022900763359</v>
+        <v>0.688888888888889</v>
       </c>
       <c r="E685" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F685" t="s">
         <v>26</v>
@@ -30663,7 +30666,7 @@
         <v>100</v>
       </c>
       <c r="M685" t="n">
-        <v>68.7</v>
+        <v>68.89</v>
       </c>
     </row>
     <row r="686">
@@ -30674,13 +30677,13 @@
         <v>91</v>
       </c>
       <c r="C686" t="n">
-        <v>1</v>
+        <v>0.999998657204063</v>
       </c>
       <c r="D686" t="n">
-        <v>0.833333333333333</v>
+        <v>0.687022900763359</v>
       </c>
       <c r="E686" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="F686" t="s">
         <v>26</v>
@@ -30704,7 +30707,7 @@
         <v>100</v>
       </c>
       <c r="M686" t="n">
-        <v>83.33</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="687">
@@ -30715,13 +30718,13 @@
         <v>91</v>
       </c>
       <c r="C687" t="n">
-        <v>0.917330588829083</v>
+        <v>1</v>
       </c>
       <c r="D687" t="n">
-        <v>0.544444444444444</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="E687" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F687" t="s">
         <v>26</v>
@@ -30742,10 +30745,10 @@
         <v>20</v>
       </c>
       <c r="L687" t="n">
-        <v>91.73</v>
+        <v>100</v>
       </c>
       <c r="M687" t="n">
-        <v>54.44</v>
+        <v>83.33</v>
       </c>
     </row>
     <row r="688">
@@ -30756,13 +30759,13 @@
         <v>91</v>
       </c>
       <c r="C688" t="n">
-        <v>1</v>
+        <v>0.917330588829083</v>
       </c>
       <c r="D688" t="n">
-        <v>0.803230543318649</v>
+        <v>0.544444444444444</v>
       </c>
       <c r="E688" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="F688" t="s">
         <v>26</v>
@@ -30783,10 +30786,10 @@
         <v>20</v>
       </c>
       <c r="L688" t="n">
-        <v>100</v>
+        <v>91.73</v>
       </c>
       <c r="M688" t="n">
-        <v>80.32</v>
+        <v>54.44</v>
       </c>
     </row>
     <row r="689">
@@ -30797,13 +30800,13 @@
         <v>91</v>
       </c>
       <c r="C689" t="n">
-        <v>0.967051206290998</v>
+        <v>1</v>
       </c>
       <c r="D689" t="n">
-        <v>0.6875</v>
+        <v>0.803230543318649</v>
       </c>
       <c r="E689" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="F689" t="s">
         <v>26</v>
@@ -30824,10 +30827,10 @@
         <v>20</v>
       </c>
       <c r="L689" t="n">
-        <v>96.71</v>
+        <v>100</v>
       </c>
       <c r="M689" t="n">
-        <v>68.75</v>
+        <v>80.32</v>
       </c>
     </row>
     <row r="690">
@@ -30838,13 +30841,13 @@
         <v>91</v>
       </c>
       <c r="C690" t="n">
-        <v>0.965164576256294</v>
+        <v>0.967051206290998</v>
       </c>
       <c r="D690" t="n">
-        <v>0.534883720930233</v>
+        <v>0.6875</v>
       </c>
       <c r="E690" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F690" t="s">
         <v>26</v>
@@ -30865,10 +30868,10 @@
         <v>20</v>
       </c>
       <c r="L690" t="n">
-        <v>96.52</v>
+        <v>96.71</v>
       </c>
       <c r="M690" t="n">
-        <v>53.49</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="691">
@@ -30879,13 +30882,13 @@
         <v>91</v>
       </c>
       <c r="C691" t="n">
-        <v>1</v>
+        <v>0.965164576256294</v>
       </c>
       <c r="D691" t="n">
-        <v>0.993506493506494</v>
+        <v>0.534883720930233</v>
       </c>
       <c r="E691" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F691" t="s">
         <v>26</v>
@@ -30906,10 +30909,10 @@
         <v>20</v>
       </c>
       <c r="L691" t="n">
-        <v>100</v>
+        <v>96.52</v>
       </c>
       <c r="M691" t="n">
-        <v>99.35</v>
+        <v>53.49</v>
       </c>
     </row>
     <row r="692">
@@ -30917,19 +30920,19 @@
         <v>730</v>
       </c>
       <c r="B692" t="n">
-        <v>912</v>
+        <v>91</v>
       </c>
       <c r="C692" t="n">
-        <v>0.113881486348322</v>
+        <v>1</v>
       </c>
       <c r="D692" t="n">
-        <v>0.0307692307692308</v>
+        <v>0.993506493506494</v>
       </c>
       <c r="E692" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F692" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
       <c r="G692" t="s">
         <v>20</v>
@@ -30938,19 +30941,19 @@
         <v>15</v>
       </c>
       <c r="I692" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J692" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K692" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L692" t="n">
-        <v>11.39</v>
+        <v>100</v>
       </c>
       <c r="M692" t="n">
-        <v>3.08</v>
+        <v>99.35</v>
       </c>
     </row>
     <row r="693">
@@ -30961,13 +30964,13 @@
         <v>912</v>
       </c>
       <c r="C693" t="n">
-        <v>0.250813677934436</v>
+        <v>0.113881486348322</v>
       </c>
       <c r="D693" t="n">
-        <v>0.108910891089109</v>
+        <v>0.0307692307692308</v>
       </c>
       <c r="E693" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F693" t="s">
         <v>129</v>
@@ -30988,10 +30991,10 @@
         <v>15</v>
       </c>
       <c r="L693" t="n">
-        <v>25.08</v>
+        <v>11.39</v>
       </c>
       <c r="M693" t="n">
-        <v>10.89</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="694">
@@ -30999,19 +31002,19 @@
         <v>732</v>
       </c>
       <c r="B694" t="n">
-        <v>936</v>
+        <v>912</v>
       </c>
       <c r="C694" t="n">
-        <v>0.0622450845981425</v>
+        <v>0.250813677934436</v>
       </c>
       <c r="D694" t="n">
-        <v>0</v>
+        <v>0.108910891089109</v>
       </c>
       <c r="E694" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F694" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="G694" t="s">
         <v>20</v>
@@ -31020,7 +31023,7 @@
         <v>15</v>
       </c>
       <c r="I694" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J694" t="s">
         <v>22</v>
@@ -31029,10 +31032,10 @@
         <v>15</v>
       </c>
       <c r="L694" t="n">
-        <v>6.22</v>
+        <v>25.08</v>
       </c>
       <c r="M694" t="n">
-        <v>0</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="695">
@@ -31043,13 +31046,13 @@
         <v>936</v>
       </c>
       <c r="C695" t="n">
-        <v>0.0546305700122455</v>
+        <v>0.0622450845981425</v>
       </c>
       <c r="D695" t="n">
-        <v>0.0204081632653061</v>
+        <v>0</v>
       </c>
       <c r="E695" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F695" t="s">
         <v>90</v>
@@ -31070,10 +31073,10 @@
         <v>15</v>
       </c>
       <c r="L695" t="n">
-        <v>5.46</v>
+        <v>6.22</v>
       </c>
       <c r="M695" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="696">
@@ -31084,16 +31087,16 @@
         <v>936</v>
       </c>
       <c r="C696" t="n">
-        <v>0.0557624323820824</v>
+        <v>0.0546305700122455</v>
       </c>
       <c r="D696" t="n">
-        <v>0</v>
+        <v>0.0204081632653061</v>
       </c>
       <c r="E696" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F696" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G696" t="s">
         <v>20</v>
@@ -31111,10 +31114,10 @@
         <v>15</v>
       </c>
       <c r="L696" t="n">
-        <v>5.58</v>
+        <v>5.46</v>
       </c>
       <c r="M696" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="697">
@@ -31122,19 +31125,19 @@
         <v>735</v>
       </c>
       <c r="B697" t="n">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="C697" t="n">
-        <v>0.0750371038259353</v>
+        <v>0.0557624323820824</v>
       </c>
       <c r="D697" t="n">
         <v>0</v>
       </c>
       <c r="E697" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F697" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="G697" t="s">
         <v>20</v>
@@ -31143,7 +31146,7 @@
         <v>15</v>
       </c>
       <c r="I697" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J697" t="s">
         <v>22</v>
@@ -31152,7 +31155,7 @@
         <v>15</v>
       </c>
       <c r="L697" t="n">
-        <v>7.5</v>
+        <v>5.58</v>
       </c>
       <c r="M697" t="n">
         <v>0</v>
@@ -31166,13 +31169,13 @@
         <v>939</v>
       </c>
       <c r="C698" t="n">
-        <v>0.0632909297051044</v>
+        <v>0.0750371038259353</v>
       </c>
       <c r="D698" t="n">
         <v>0</v>
       </c>
       <c r="E698" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F698" t="s">
         <v>14</v>
@@ -31193,7 +31196,7 @@
         <v>15</v>
       </c>
       <c r="L698" t="n">
-        <v>6.33</v>
+        <v>7.5</v>
       </c>
       <c r="M698" t="n">
         <v>0</v>
@@ -31204,19 +31207,19 @@
         <v>737</v>
       </c>
       <c r="B699" t="n">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="C699" t="n">
-        <v>0.0801643741524908</v>
+        <v>0.0632909297051044</v>
       </c>
       <c r="D699" t="n">
-        <v>0.0769230769230769</v>
+        <v>0</v>
       </c>
       <c r="E699" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F699" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="G699" t="s">
         <v>20</v>
@@ -31225,7 +31228,7 @@
         <v>15</v>
       </c>
       <c r="I699" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J699" t="s">
         <v>22</v>
@@ -31234,10 +31237,10 @@
         <v>15</v>
       </c>
       <c r="L699" t="n">
-        <v>8.02</v>
+        <v>6.33</v>
       </c>
       <c r="M699" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="700">
@@ -31248,13 +31251,13 @@
         <v>952</v>
       </c>
       <c r="C700" t="n">
-        <v>0.063686498275921</v>
+        <v>0.0801643741524908</v>
       </c>
       <c r="D700" t="n">
-        <v>0</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E700" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F700" t="s">
         <v>100</v>
@@ -31275,10 +31278,10 @@
         <v>15</v>
       </c>
       <c r="L700" t="n">
-        <v>6.37</v>
+        <v>8.02</v>
       </c>
       <c r="M700" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="701">
@@ -31289,13 +31292,13 @@
         <v>952</v>
       </c>
       <c r="C701" t="n">
-        <v>0.0750422754326339</v>
+        <v>0.063686498275921</v>
       </c>
       <c r="D701" t="n">
         <v>0</v>
       </c>
       <c r="E701" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F701" t="s">
         <v>100</v>
@@ -31316,7 +31319,7 @@
         <v>15</v>
       </c>
       <c r="L701" t="n">
-        <v>7.5</v>
+        <v>6.37</v>
       </c>
       <c r="M701" t="n">
         <v>0</v>
@@ -31327,19 +31330,19 @@
         <v>740</v>
       </c>
       <c r="B702" t="n">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="C702" t="n">
-        <v>0.0611416145707814</v>
+        <v>0.0750422754326339</v>
       </c>
       <c r="D702" t="n">
         <v>0</v>
       </c>
       <c r="E702" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F702" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G702" t="s">
         <v>20</v>
@@ -31348,7 +31351,7 @@
         <v>15</v>
       </c>
       <c r="I702" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J702" t="s">
         <v>22</v>
@@ -31357,7 +31360,7 @@
         <v>15</v>
       </c>
       <c r="L702" t="n">
-        <v>6.11</v>
+        <v>7.5</v>
       </c>
       <c r="M702" t="n">
         <v>0</v>
@@ -31368,19 +31371,19 @@
         <v>741</v>
       </c>
       <c r="B703" t="n">
-        <v>996</v>
+        <v>963</v>
       </c>
       <c r="C703" t="n">
-        <v>0.0877178321907405</v>
+        <v>0.0611416145707814</v>
       </c>
       <c r="D703" t="n">
         <v>0</v>
       </c>
       <c r="E703" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F703" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="G703" t="s">
         <v>20</v>
@@ -31389,16 +31392,16 @@
         <v>15</v>
       </c>
       <c r="I703" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J703" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K703" t="s">
         <v>15</v>
       </c>
       <c r="L703" t="n">
-        <v>8.77</v>
+        <v>6.11</v>
       </c>
       <c r="M703" t="n">
         <v>0</v>
@@ -31412,13 +31415,13 @@
         <v>996</v>
       </c>
       <c r="C704" t="n">
-        <v>0.0772955990435405</v>
+        <v>0.0877178321907405</v>
       </c>
       <c r="D704" t="n">
         <v>0</v>
       </c>
       <c r="E704" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F704" t="s">
         <v>14</v>
@@ -31439,7 +31442,7 @@
         <v>15</v>
       </c>
       <c r="L704" t="n">
-        <v>7.73</v>
+        <v>8.77</v>
       </c>
       <c r="M704" t="n">
         <v>0</v>
@@ -31453,13 +31456,13 @@
         <v>996</v>
       </c>
       <c r="C705" t="n">
-        <v>0.132560704084967</v>
+        <v>0.0772955990435405</v>
       </c>
       <c r="D705" t="n">
         <v>0</v>
       </c>
       <c r="E705" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F705" t="s">
         <v>14</v>
@@ -31480,7 +31483,7 @@
         <v>15</v>
       </c>
       <c r="L705" t="n">
-        <v>13.26</v>
+        <v>7.73</v>
       </c>
       <c r="M705" t="n">
         <v>0</v>
@@ -31494,13 +31497,13 @@
         <v>996</v>
       </c>
       <c r="C706" t="n">
-        <v>0.143379028469796</v>
+        <v>0.132560704084967</v>
       </c>
       <c r="D706" t="n">
         <v>0</v>
       </c>
       <c r="E706" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F706" t="s">
         <v>14</v>
@@ -31521,7 +31524,7 @@
         <v>15</v>
       </c>
       <c r="L706" t="n">
-        <v>14.34</v>
+        <v>13.26</v>
       </c>
       <c r="M706" t="n">
         <v>0</v>
@@ -31535,13 +31538,13 @@
         <v>996</v>
       </c>
       <c r="C707" t="n">
-        <v>0.201816665935531</v>
+        <v>0.143379028469796</v>
       </c>
       <c r="D707" t="n">
         <v>0</v>
       </c>
       <c r="E707" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F707" t="s">
         <v>14</v>
@@ -31562,7 +31565,7 @@
         <v>15</v>
       </c>
       <c r="L707" t="n">
-        <v>20.18</v>
+        <v>14.34</v>
       </c>
       <c r="M707" t="n">
         <v>0</v>
@@ -31576,7 +31579,7 @@
         <v>996</v>
       </c>
       <c r="C708" t="n">
-        <v>0.145121400574626</v>
+        <v>0.201816665935531</v>
       </c>
       <c r="D708" t="n">
         <v>0</v>
@@ -31603,9 +31606,50 @@
         <v>15</v>
       </c>
       <c r="L708" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="M708" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="s">
+        <v>747</v>
+      </c>
+      <c r="B709" t="n">
+        <v>996</v>
+      </c>
+      <c r="C709" t="n">
+        <v>0.145121400574626</v>
+      </c>
+      <c r="D709" t="n">
+        <v>0</v>
+      </c>
+      <c r="E709" t="n">
+        <v>6</v>
+      </c>
+      <c r="F709" t="s">
+        <v>14</v>
+      </c>
+      <c r="G709" t="s">
+        <v>20</v>
+      </c>
+      <c r="H709" t="s">
+        <v>15</v>
+      </c>
+      <c r="I709" t="s">
+        <v>21</v>
+      </c>
+      <c r="J709" t="s">
+        <v>17</v>
+      </c>
+      <c r="K709" t="s">
+        <v>15</v>
+      </c>
+      <c r="L709" t="n">
         <v>14.51</v>
       </c>
-      <c r="M708" t="n">
+      <c r="M709" t="n">
         <v>0</v>
       </c>
     </row>
